--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/主角_装备配置表_Protagonist_ProtagonistEquipmentConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/主角_装备配置表_Protagonist_ProtagonistEquipmentConfig.xlsx
@@ -2,39 +2,381 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="21">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="34">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -42,15 +384,317 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -403,7 +1047,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -413,8 +1056,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:I33"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col width="22.625" customWidth="1" style="5" min="1" max="1"/>
+    <col width="16.875" customWidth="1" style="5" min="4" max="4"/>
+    <col width="33.875" customWidth="1" style="5" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -510,48 +1158,48 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" customFormat="1" s="1">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>EquipId</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>EquipLevel</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>DisplayName</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>IconAssetId</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>ExpToNextLevel</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>ConvertExpValue</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>EffectDomain</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>EquipEffect</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -583,7 +1231,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -593,7 +1241,7 @@
           <t>Dig</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>DigCursorRadius_0.06</t>
         </is>
@@ -630,19 +1278,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F5" s="6" t="n">
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Dig</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>DigCursorRadius_0.12</t>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>DigCursorRadius_0.16</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -677,19 +1323,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F6" s="6" t="n">
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Dig</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>DigCursorRadius_0.18</t>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>DigCursorRadius_0.26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -724,19 +1368,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F7" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Dig</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>DigCursorRadius_0.24</t>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>DigCursorRadius_0.36</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -766,19 +1408,17 @@
           <t>Icon_IronShovel</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F8" s="6" t="n">
+        <v>5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Dig</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>DigCursorRadius_0.30</t>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>DigCursorRadius_0.46</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -813,7 +1453,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -823,7 +1463,7 @@
           <t>Dig</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>GraveSpawnWeightBonus_Q4_10|GraveSpawnWeightBonus_Q5_10|GraveSpawnWeightBonus_Q6_10</t>
         </is>
@@ -860,17 +1500,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F10" s="6" t="n">
+        <v>2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Dig</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>GraveSpawnWeightBonus_Q4_20|GraveSpawnWeightBonus_Q5_20|GraveSpawnWeightBonus_Q6_20</t>
         </is>
@@ -907,17 +1545,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F11" s="6" t="n">
+        <v>3</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>Dig</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>GraveSpawnWeightBonus_Q4_30|GraveSpawnWeightBonus_Q5_30|GraveSpawnWeightBonus_Q6_30</t>
         </is>
@@ -954,17 +1590,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F12" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Dig</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>GraveSpawnWeightBonus_Q4_40|GraveSpawnWeightBonus_Q5_40|GraveSpawnWeightBonus_Q6_40</t>
         </is>
@@ -997,17 +1631,15 @@
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F13" s="6" t="n">
+        <v>5</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>Dig</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>GraveSpawnWeightBonus_Q4_50|GraveSpawnWeightBonus_Q5_50|GraveSpawnWeightBonus_Q6_50</t>
         </is>
@@ -1017,6 +1649,687 @@
           <t>每级增加Q4/Q5/Q6生成权重10（满级）</t>
         </is>
       </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Equip_Explosives</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>炸药</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Icon_Explosives</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>DigOnGraveClear_1|ExplosiveThrowRadius_3|ExplosiveBlastRadius_1.5|ExplosiveBlastDamage_13|ExplosiveFlightSec_0.5|ExplosiveFuseSec_0.8|ExplosiveRingSec_0.5</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>从挖开坟墓后，向周围随机丢出1个炸药桶，落地后爆炸</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Equip_Explosives</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>炸药</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Icon_Explosives</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>DigOnGraveClear_1|ExplosiveThrowRadius_3|ExplosiveBlastRadius_1.5|ExplosiveBlastDamage_18|ExplosiveFlightSec_0.5|ExplosiveFuseSec_0.8|ExplosiveRingSec_0.5</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>从挖开坟墓后，向周围随机丢出1个炸药桶，落地后爆炸</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Equip_Explosives</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>炸药</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Icon_Explosives</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>DigOnGraveClear_1|ExplosiveThrowRadius_3|ExplosiveBlastRadius_1.5|ExplosiveBlastDamage_23|ExplosiveFlightSec_0.5|ExplosiveFuseSec_0.8|ExplosiveRingSec_0.5</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>从挖开坟墓后，向周围随机丢出1个炸药桶，落地后爆炸</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Equip_Explosives</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>炸药</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Icon_Explosives</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>DigOnGraveClear_1|ExplosiveThrowRadius_3|ExplosiveBlastRadius_1.5|ExplosiveBlastDamage_28|ExplosiveFlightSec_0.5|ExplosiveFuseSec_0.8|ExplosiveRingSec_0.5</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>从挖开坟墓后，向周围随机丢出1个炸药桶，落地后爆炸</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Equip_Explosives</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>炸药</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Icon_Explosives</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>DigOnGraveClear_1|ExplosiveThrowRadius_3|ExplosiveBlastRadius_1.5|ExplosiveBlastDamage_33|ExplosiveFlightSec_0.5|ExplosiveFuseSec_0.8|ExplosiveRingSec_0.5</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>从挖开坟墓后，向周围随机丢出1个炸药桶，落地后爆炸</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Equip_Elctr</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>引雷</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Icon_Elctr</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>DigLightningIntervalSec_15|DigLightningFrameSec_0.05|DigLightningPreviewSec_2</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>挖坟倒计时，每隔15秒，天上落下一个闪电，会随机命中一个坟墓产出士兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Equip_Elctr</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>引雷</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Icon_Elctr</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>DigLightningIntervalSec_13|DigLightningFrameSec_0.05|DigLightningPreviewSec_2</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>挖坟倒计时，每隔13秒，天上落下一个闪电，会随机命中一个坟墓产出士兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Equip_Elctr</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>引雷</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Icon_Elctr</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>DigLightningIntervalSec_11|DigLightningFrameSec_0.05|DigLightningPreviewSec_2</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>挖坟倒计时，每隔11秒，天上落下一个闪电，会随机命中一个坟墓产出士兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Equip_Elctr</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>引雷</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Icon_Elctr</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>DigLightningIntervalSec_9|DigLightningFrameSec_0.05|DigLightningPreviewSec_2</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>挖坟倒计时，每隔9秒，天上落下一个闪电，会随机命中一个坟墓产出士兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Equip_Elctr</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>引雷</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Icon_Elctr</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>DigLightningIntervalSec_7|DigLightningFrameSec_0.05|DigLightningPreviewSec_2</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>挖坟倒计时，每隔7秒，天上落下一个闪电，会随机命中一个坟墓产出士兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Equip_Detector</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>探测器</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Icon_Detector</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>DigProcessSpawnCountBonus_1</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>每级增加过程生成坟墓数量+1（1级）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Equip_Detector</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>探测器</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Icon_Detector</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>DigProcessSpawnCountBonus_2</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>每级增加过程生成坟墓数量+1（2级）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Equip_Detector</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>探测器</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Icon_Detector</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>DigProcessSpawnCountBonus_3</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>每级增加过程生成坟墓数量+1（3级）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Equip_Detector</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>探测器</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Icon_Detector</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>DigProcessSpawnCountBonus_4</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>每级增加过程生成坟墓数量+1（4级）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Equip_Detector</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>探测器</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Icon_Detector</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>DigProcessSpawnCountBonus_5</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>每级增加过程生成坟墓数量+1（满级）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="F29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="F30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="F31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="F32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="F33" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/主角_装备配置表_Protagonist_ProtagonistEquipmentConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/主角_装备配置表_Protagonist_ProtagonistEquipmentConfig.xlsx
@@ -16,14 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="21">
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -176,7 +169,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill/>
     </fill>
@@ -186,6 +179,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -484,165 +483,168 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1056,12 +1058,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="22.625" customWidth="1" style="5" min="1" max="1"/>
-    <col width="16.875" customWidth="1" style="5" min="4" max="4"/>
-    <col width="33.875" customWidth="1" style="5" min="8" max="8"/>
+    <col width="22.625" customWidth="1" style="4" min="1" max="1"/>
+    <col width="16.875" customWidth="1" style="4" min="4" max="4"/>
+    <col width="33.875" customWidth="1" style="4" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1231,7 +1233,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1241,7 +1243,7 @@
           <t>Dig</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>DigCursorRadius_0.06</t>
         </is>
@@ -1278,7 +1280,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="5" t="n">
         <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
@@ -1286,7 +1288,7 @@
           <t>Dig</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>DigCursorRadius_0.16</t>
         </is>
@@ -1323,7 +1325,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="5" t="n">
         <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
@@ -1331,7 +1333,7 @@
           <t>Dig</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>DigCursorRadius_0.26</t>
         </is>
@@ -1368,7 +1370,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="5" t="n">
         <v>4</v>
       </c>
       <c r="G7" t="inlineStr">
@@ -1376,7 +1378,7 @@
           <t>Dig</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>DigCursorRadius_0.36</t>
         </is>
@@ -1408,7 +1410,7 @@
           <t>Icon_IronShovel</t>
         </is>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G8" t="inlineStr">
@@ -1416,7 +1418,7 @@
           <t>Dig</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>DigCursorRadius_0.46</t>
         </is>
@@ -1453,7 +1455,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1463,7 +1465,7 @@
           <t>Dig</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>GraveSpawnWeightBonus_Q4_10|GraveSpawnWeightBonus_Q5_10|GraveSpawnWeightBonus_Q6_10</t>
         </is>
@@ -1500,7 +1502,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="5" t="n">
         <v>2</v>
       </c>
       <c r="G10" t="inlineStr">
@@ -1508,7 +1510,7 @@
           <t>Dig</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>GraveSpawnWeightBonus_Q4_20|GraveSpawnWeightBonus_Q5_20|GraveSpawnWeightBonus_Q6_20</t>
         </is>
@@ -1545,7 +1547,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="5" t="n">
         <v>3</v>
       </c>
       <c r="G11" t="inlineStr">
@@ -1553,7 +1555,7 @@
           <t>Dig</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>GraveSpawnWeightBonus_Q4_30|GraveSpawnWeightBonus_Q5_30|GraveSpawnWeightBonus_Q6_30</t>
         </is>
@@ -1590,7 +1592,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="5" t="n">
         <v>4</v>
       </c>
       <c r="G12" t="inlineStr">
@@ -1598,7 +1600,7 @@
           <t>Dig</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>GraveSpawnWeightBonus_Q4_40|GraveSpawnWeightBonus_Q5_40|GraveSpawnWeightBonus_Q6_40</t>
         </is>
@@ -1631,7 +1633,7 @@
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" s="6" t="n">
+      <c r="F13" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G13" t="inlineStr">
@@ -1639,7 +1641,7 @@
           <t>Dig</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>GraveSpawnWeightBonus_Q4_50|GraveSpawnWeightBonus_Q5_50|GraveSpawnWeightBonus_Q6_50</t>
         </is>
@@ -1676,7 +1678,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1686,7 +1688,7 @@
           <t>Dig</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>DigOnGraveClear_1|ExplosiveThrowRadius_3|ExplosiveBlastRadius_1.5|ExplosiveBlastDamage_13|ExplosiveFlightSec_0.5|ExplosiveFuseSec_0.8|ExplosiveRingSec_0.5</t>
         </is>
@@ -1723,7 +1725,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F15" s="5" t="n">
         <v>2</v>
       </c>
       <c r="G15" t="inlineStr">
@@ -1731,7 +1733,7 @@
           <t>Dig</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>DigOnGraveClear_1|ExplosiveThrowRadius_3|ExplosiveBlastRadius_1.5|ExplosiveBlastDamage_18|ExplosiveFlightSec_0.5|ExplosiveFuseSec_0.8|ExplosiveRingSec_0.5</t>
         </is>
@@ -1768,7 +1770,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F16" s="5" t="n">
         <v>3</v>
       </c>
       <c r="G16" t="inlineStr">
@@ -1776,7 +1778,7 @@
           <t>Dig</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>DigOnGraveClear_1|ExplosiveThrowRadius_3|ExplosiveBlastRadius_1.5|ExplosiveBlastDamage_23|ExplosiveFlightSec_0.5|ExplosiveFuseSec_0.8|ExplosiveRingSec_0.5</t>
         </is>
@@ -1813,7 +1815,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="F17" s="5" t="n">
         <v>4</v>
       </c>
       <c r="G17" t="inlineStr">
@@ -1821,7 +1823,7 @@
           <t>Dig</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>DigOnGraveClear_1|ExplosiveThrowRadius_3|ExplosiveBlastRadius_1.5|ExplosiveBlastDamage_28|ExplosiveFlightSec_0.5|ExplosiveFuseSec_0.8|ExplosiveRingSec_0.5</t>
         </is>
@@ -1853,7 +1855,7 @@
           <t>Icon_Explosives</t>
         </is>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="F18" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G18" t="inlineStr">
@@ -1861,7 +1863,7 @@
           <t>Dig</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>DigOnGraveClear_1|ExplosiveThrowRadius_3|ExplosiveBlastRadius_1.5|ExplosiveBlastDamage_33|ExplosiveFlightSec_0.5|ExplosiveFuseSec_0.8|ExplosiveRingSec_0.5</t>
         </is>
@@ -1898,7 +1900,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1908,7 +1910,7 @@
           <t>Dig</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>DigLightningIntervalSec_15|DigLightningFrameSec_0.05|DigLightningPreviewSec_2</t>
         </is>
@@ -1945,7 +1947,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="F20" s="5" t="n">
         <v>2</v>
       </c>
       <c r="G20" t="inlineStr">
@@ -1953,7 +1955,7 @@
           <t>Dig</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>DigLightningIntervalSec_13|DigLightningFrameSec_0.05|DigLightningPreviewSec_2</t>
         </is>
@@ -1990,7 +1992,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="F21" s="5" t="n">
         <v>3</v>
       </c>
       <c r="G21" t="inlineStr">
@@ -1998,7 +2000,7 @@
           <t>Dig</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>DigLightningIntervalSec_11|DigLightningFrameSec_0.05|DigLightningPreviewSec_2</t>
         </is>
@@ -2035,7 +2037,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="F22" s="5" t="n">
         <v>4</v>
       </c>
       <c r="G22" t="inlineStr">
@@ -2043,7 +2045,7 @@
           <t>Dig</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>DigLightningIntervalSec_9|DigLightningFrameSec_0.05|DigLightningPreviewSec_2</t>
         </is>
@@ -2075,7 +2077,7 @@
           <t>Icon_Elctr</t>
         </is>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="F23" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G23" t="inlineStr">
@@ -2083,7 +2085,7 @@
           <t>Dig</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>DigLightningIntervalSec_7|DigLightningFrameSec_0.05|DigLightningPreviewSec_2</t>
         </is>
@@ -2120,7 +2122,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2137,7 +2139,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>每级增加过程生成坟墓数量+1（1级）</t>
+          <t>每级增加挖坟过程生成坟墓数量+1（1级）</t>
         </is>
       </c>
     </row>
@@ -2167,7 +2169,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="F25" s="5" t="n">
         <v>2</v>
       </c>
       <c r="G25" t="inlineStr">
@@ -2182,7 +2184,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>每级增加过程生成坟墓数量+1（2级）</t>
+          <t>每级增加挖坟过程生成坟墓数量+1（2级）</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2214,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="F26" s="5" t="n">
         <v>3</v>
       </c>
       <c r="G26" t="inlineStr">
@@ -2227,7 +2229,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>每级增加过程生成坟墓数量+1（3级）</t>
+          <t>每级增加挖坟过程生成坟墓数量+1（3级）</t>
         </is>
       </c>
     </row>
@@ -2257,7 +2259,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="F27" s="5" t="n">
         <v>4</v>
       </c>
       <c r="G27" t="inlineStr">
@@ -2272,7 +2274,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>每级增加过程生成坟墓数量+1（4级）</t>
+          <t>每级增加挖坟过程生成坟墓数量+1（4级）</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2299,7 @@
           <t>Icon_Detector</t>
         </is>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="F28" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G28" t="inlineStr">
@@ -2312,24 +2314,684 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>每级增加过程生成坟墓数量+1（满级）</t>
+          <t>每级增加挖坟过程生成坟墓数量+1（满级）</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="F29" s="6" t="n"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Equip_HumanToken</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>人类信物</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Icon_HumanToken</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>GraveSpawnWeightBonus_Q16_10|GraveSpawnWeightBonus_Q17_10|GraveSpawnWeightBonus_Q18_10|GraveSpawnWeightBonus_Q19_10</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>增加发现人类坟墓的概率</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="F30" s="6" t="n"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Equip_HumanToken</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>人类信物</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Icon_HumanToken</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>GraveSpawnWeightBonus_Q16_15|GraveSpawnWeightBonus_Q17_15|GraveSpawnWeightBonus_Q18_15|GraveSpawnWeightBonus_Q19_15</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>增加发现人类坟墓的概率</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="F31" s="6" t="n"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Equip_HumanToken</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>人类信物</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Icon_HumanToken</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>GraveSpawnWeightBonus_Q16_20|GraveSpawnWeightBonus_Q17_20|GraveSpawnWeightBonus_Q18_20|GraveSpawnWeightBonus_Q19_20</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>增加发现人类坟墓的概率</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="F32" s="6" t="n"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Equip_HumanToken</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>人类信物</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Icon_HumanToken</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>GraveSpawnWeightBonus_Q16_25|GraveSpawnWeightBonus_Q17_25|GraveSpawnWeightBonus_Q18_25|GraveSpawnWeightBonus_Q19_25</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>增加发现人类坟墓的概率</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="F33" s="6" t="n"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Equip_HumanToken</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>人类信物</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Icon_HumanToken</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>GraveSpawnWeightBonus_Q16_30|GraveSpawnWeightBonus_Q17_30|GraveSpawnWeightBonus_Q18_30|GraveSpawnWeightBonus_Q19_30</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>增加发现人类坟墓的概率</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Equip_ElfToken</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>精灵信物</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Icon_ElfToken</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>GraveSpawnWeightBonus_Q20_10|GraveSpawnWeightBonus_Q21_10|GraveSpawnWeightBonus_Q22_10|GraveSpawnWeightBonus_Q23_10</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>增加发现精灵族坟墓的概率</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Equip_ElfToken</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>精灵信物</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Icon_ElfToken</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>GraveSpawnWeightBonus_Q20_15|GraveSpawnWeightBonus_Q21_15|GraveSpawnWeightBonus_Q22_15|GraveSpawnWeightBonus_Q23_15</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>增加发现精灵族坟墓的概率</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Equip_ElfToken</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>精灵信物</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Icon_ElfToken</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>GraveSpawnWeightBonus_Q20_20|GraveSpawnWeightBonus_Q21_20|GraveSpawnWeightBonus_Q22_20|GraveSpawnWeightBonus_Q23_20</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>增加发现精灵族坟墓的概率</t>
+        </is>
+      </c>
+      <c r="J36" s="7" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Equip_ElfToken</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>精灵信物</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Icon_ElfToken</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>GraveSpawnWeightBonus_Q20_25|GraveSpawnWeightBonus_Q21_25|GraveSpawnWeightBonus_Q22_25|GraveSpawnWeightBonus_Q23_25</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>增加发现精灵族坟墓的概率</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Equip_ElfToken</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>精灵信物</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Icon_ElfToken</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>GraveSpawnWeightBonus_Q20_30|GraveSpawnWeightBonus_Q21_30|GraveSpawnWeightBonus_Q22_30|GraveSpawnWeightBonus_Q23_30</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>增加发现精灵族坟墓的概率</t>
+        </is>
+      </c>
+      <c r="J38" s="7" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Equip_OrcToken</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>兽人信物</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Icon_OrcToken</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>GraveSpawnWeightBonus_Q24_10|GraveSpawnWeightBonus_Q25_10|GraveSpawnWeightBonus_Q26_10|GraveSpawnWeightBonus_Q27_10</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>增加发现兽人坟墓的概率</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Equip_OrcToken</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>兽人信物</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Icon_OrcToken</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>GraveSpawnWeightBonus_Q24_15|GraveSpawnWeightBonus_Q25_15|GraveSpawnWeightBonus_Q26_15|GraveSpawnWeightBonus_Q27_15</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>增加发现兽人坟墓的概率</t>
+        </is>
+      </c>
+      <c r="J40" s="7" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Equip_OrcToken</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>兽人信物</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Icon_OrcToken</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>GraveSpawnWeightBonus_Q24_20|GraveSpawnWeightBonus_Q25_20|GraveSpawnWeightBonus_Q26_20|GraveSpawnWeightBonus_Q27_20</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>增加发现兽人坟墓的概率</t>
+        </is>
+      </c>
+      <c r="J41" s="7" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Equip_OrcToken</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>兽人信物</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Icon_OrcToken</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>GraveSpawnWeightBonus_Q24_25|GraveSpawnWeightBonus_Q25_25|GraveSpawnWeightBonus_Q26_25|GraveSpawnWeightBonus_Q27_25</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>增加发现兽人坟墓的概率</t>
+        </is>
+      </c>
+      <c r="J42" s="7" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Equip_OrcToken</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>兽人信物</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Icon_OrcToken</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>GraveSpawnWeightBonus_Q24_30|GraveSpawnWeightBonus_Q25_30|GraveSpawnWeightBonus_Q26_30|GraveSpawnWeightBonus_Q27_30</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>增加发现兽人坟墓的概率</t>
+        </is>
+      </c>
+      <c r="J43" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
